--- a/public/templates/leave-card.xlsx
+++ b/public/templates/leave-card.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIS\LMS\spana-yt\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6335D1BA-C4D2-470D-B023-7E64C015F2CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DA141F-A934-41A1-BB8F-4A5C897DA3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Level Card  (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Level Card '!$A$1:$K$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Level Card '!$A$1:$K$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
   <si>
     <t>ថ្ងៃដាក់ពាក្យ</t>
   </si>
@@ -520,122 +520,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,7 +1099,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A5:K75"/>
+  <dimension ref="A5:K28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1115,162 +1115,162 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.65">
-      <c r="A6" s="20" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
+      <c r="A6" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19" t="s">
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="19"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="21" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="30"/>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="19" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="19"/>
+      <c r="J9" s="26"/>
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
     </row>
     <row r="11" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="39"/>
+      <c r="D12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="37" t="s">
+      <c r="I12" s="42"/>
+      <c r="J12" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="38"/>
+      <c r="K12" s="46"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="27" t="s">
+      <c r="A13" s="36"/>
+      <c r="B13" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="48"/>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
       <c r="H14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1297,908 +1297,249 @@
       <c r="J15" s="8"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A17" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+    </row>
+    <row r="18" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
+    </row>
+    <row r="19" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A19" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="K19" s="46"/>
+    </row>
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A20" s="36"/>
+      <c r="B20" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="48"/>
+    </row>
+    <row r="21" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A21" s="37"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="7"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="8"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A23" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+    </row>
+    <row r="25" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A25" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="42"/>
+      <c r="J25" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="K25" s="46"/>
+    </row>
+    <row r="26" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A26" s="36"/>
+      <c r="B26" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="48"/>
+    </row>
+    <row r="27" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A27" s="37"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="7"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="8"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="6"/>
-    </row>
-    <row r="37" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="6"/>
-    </row>
-    <row r="38" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="6"/>
-    </row>
-    <row r="39" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="6"/>
-    </row>
-    <row r="40" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-    </row>
-    <row r="42" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="16"/>
-    </row>
-    <row r="43" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="J43" s="21"/>
-      <c r="K43" s="16"/>
-    </row>
-    <row r="44" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="19"/>
-      <c r="K44" s="16"/>
-    </row>
-    <row r="45" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A45" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-    </row>
-    <row r="46" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="57"/>
-    </row>
-    <row r="47" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A47" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="44"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="38"/>
-    </row>
-    <row r="48" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A48" s="29"/>
-      <c r="B48" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="40"/>
-    </row>
-    <row r="49" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A49" s="30"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="6"/>
-    </row>
-    <row r="51" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="6"/>
-    </row>
-    <row r="52" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="42"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="6"/>
-    </row>
-    <row r="53" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="6"/>
-    </row>
-    <row r="54" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="43"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="6"/>
-    </row>
-    <row r="55" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="6"/>
-    </row>
-    <row r="56" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="6"/>
-    </row>
-    <row r="57" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="6"/>
-    </row>
-    <row r="58" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="6"/>
-    </row>
-    <row r="59" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="50"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="6"/>
-    </row>
-    <row r="60" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A60" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="49"/>
-      <c r="K60" s="49"/>
-    </row>
-    <row r="61" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A61" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-    </row>
-    <row r="62" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A62" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="H62" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="34"/>
-      <c r="J62" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="38"/>
-    </row>
-    <row r="63" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A63" s="29"/>
-      <c r="B63" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="40"/>
-    </row>
-    <row r="64" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A64" s="30"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="53"/>
-      <c r="H64" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="6"/>
-    </row>
-    <row r="66" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="6"/>
-    </row>
-    <row r="67" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="6"/>
-    </row>
-    <row r="68" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="6"/>
-    </row>
-    <row r="69" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="6"/>
-    </row>
-    <row r="70" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="6"/>
-    </row>
-    <row r="71" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="6"/>
-    </row>
-    <row r="72" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="6"/>
-    </row>
-    <row r="73" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="6"/>
-    </row>
-    <row r="74" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="6"/>
-    </row>
-    <row r="75" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="6"/>
-    </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="E62:E64"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="H62:I63"/>
-    <mergeCell ref="J62:K63"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="J47:K48"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="G47:I49"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="F47:F49"/>
+  <mergeCells count="48">
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="C13:C14"/>
@@ -2211,16 +1552,32 @@
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:K13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="J19:K20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="G19:I21"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:I26"/>
+    <mergeCell ref="J25:K26"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:D21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -2250,164 +1607,164 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.65">
-      <c r="A5" s="20" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
+      <c r="A5" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19" t="s">
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="21" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="21"/>
+      <c r="J7" s="30"/>
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="19" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="19"/>
+      <c r="J8" s="26"/>
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
     </row>
     <row r="10" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="28" t="s">
+      <c r="C11" s="39"/>
+      <c r="D11" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="37" t="s">
+      <c r="I11" s="42"/>
+      <c r="J11" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="38"/>
+      <c r="K11" s="46"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="27" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="40"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="3" t="s">
         <v>1</v>
       </c>
@@ -2708,159 +2065,159 @@
       <c r="K35" s="6"/>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19" t="s">
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="19"/>
+      <c r="J37" s="26"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="21" t="s">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="21"/>
+      <c r="J38" s="30"/>
       <c r="K38" s="16"/>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="19" t="s">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="19"/>
+      <c r="J39" s="26"/>
       <c r="K39" s="16"/>
     </row>
     <row r="40" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="57"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="34"/>
     </row>
     <row r="42" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="28" t="s">
+      <c r="C42" s="39"/>
+      <c r="D42" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="44"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="37" t="s">
+      <c r="H42" s="41"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="38"/>
+      <c r="K42" s="46"/>
     </row>
     <row r="43" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A43" s="29"/>
-      <c r="B43" s="27" t="s">
+      <c r="A43" s="36"/>
+      <c r="B43" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="40"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="48"/>
     </row>
     <row r="44" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="36"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="44"/>
       <c r="J44" s="4" t="s">
         <v>4</v>
       </c>
@@ -2875,9 +2232,9 @@
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="43"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="22"/>
       <c r="J45" s="8"/>
       <c r="K45" s="6"/>
     </row>
@@ -2888,9 +2245,9 @@
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="43"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="22"/>
       <c r="J46" s="8"/>
       <c r="K46" s="6"/>
     </row>
@@ -2901,9 +2258,9 @@
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="43"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="22"/>
       <c r="J47" s="8"/>
       <c r="K47" s="6"/>
     </row>
@@ -2914,9 +2271,9 @@
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="43"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="22"/>
       <c r="J48" s="8"/>
       <c r="K48" s="6"/>
     </row>
@@ -2927,9 +2284,9 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="43"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="22"/>
       <c r="J49" s="8"/>
       <c r="K49" s="6"/>
     </row>
@@ -2940,9 +2297,9 @@
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="52"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="25"/>
       <c r="J50" s="8"/>
       <c r="K50" s="6"/>
     </row>
@@ -2953,9 +2310,9 @@
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="52"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="25"/>
       <c r="J51" s="8"/>
       <c r="K51" s="6"/>
     </row>
@@ -2966,9 +2323,9 @@
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="52"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="25"/>
       <c r="J52" s="8"/>
       <c r="K52" s="6"/>
     </row>
@@ -2979,9 +2336,9 @@
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="52"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="25"/>
       <c r="J53" s="8"/>
       <c r="K53" s="6"/>
     </row>
@@ -2992,96 +2349,96 @@
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="52"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="25"/>
       <c r="J54" s="8"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+      <c r="K55" s="27"/>
     </row>
     <row r="56" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A56" s="24" t="s">
+      <c r="A56" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
     </row>
     <row r="57" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="28" t="s">
+      <c r="C57" s="39"/>
+      <c r="D57" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="53" t="s">
+      <c r="G57" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="H57" s="44" t="s">
+      <c r="H57" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="34"/>
-      <c r="J57" s="37" t="s">
+      <c r="I57" s="42"/>
+      <c r="J57" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="38"/>
+      <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A58" s="29"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="36"/>
+      <c r="B58" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="40"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="47"/>
+      <c r="K58" s="48"/>
     </row>
     <row r="59" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A59" s="30"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="53"/>
+      <c r="A59" s="37"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="40"/>
       <c r="H59" s="15" t="s">
         <v>1</v>
       </c>
@@ -3201,14 +2558,48 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="H57:I58"/>
+    <mergeCell ref="J57:K58"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="G42:I44"/>
+    <mergeCell ref="J42:K43"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:H8"/>
@@ -3225,48 +2616,14 @@
     <mergeCell ref="J11:K12"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G42:I44"/>
-    <mergeCell ref="J42:K43"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="H57:I58"/>
-    <mergeCell ref="J57:K58"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>

--- a/public/templates/leave-card.xlsx
+++ b/public/templates/leave-card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIS\LMS\spana-yt\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DA141F-A934-41A1-BB8F-4A5C897DA3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548E7264-7798-4974-8C39-C24873481B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Level Card  (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Level Card '!$A$1:$K$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Level Card '!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -474,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -520,6 +520,108 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -532,6 +634,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -541,101 +652,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,7 +1120,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A5:K28"/>
+  <dimension ref="A5:K40"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1115,162 +1136,162 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26" t="s">
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="24"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="30" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="30"/>
+      <c r="J8" s="26"/>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="26" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="35" t="s">
+      <c r="C12" s="37"/>
+      <c r="D12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="42"/>
-      <c r="J12" s="45" t="s">
+      <c r="I12" s="39"/>
+      <c r="J12" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="46"/>
+      <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="49" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="48"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1284,262 +1305,434 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="27" t="s">
+    <row r="15" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A17" s="28" t="s">
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+    </row>
+    <row r="21" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A21" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-    </row>
-    <row r="18" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="13" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+    </row>
+    <row r="22" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="34"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A19" s="35" t="s">
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="59"/>
+    </row>
+    <row r="23" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A23" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B23" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="35" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E23" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F23" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="G23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="45" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K19" s="46"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A20" s="36"/>
-      <c r="B20" s="49" t="s">
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A24" s="34"/>
+      <c r="B24" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C24" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="48"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="37"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="4" t="s">
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="45"/>
+    </row>
+    <row r="25" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A25" s="35"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A23" s="27" t="s">
+    <row r="26" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A26" s="19"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A27" s="19"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A28" s="19"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A29" s="19"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A31" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-    </row>
-    <row r="24" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A24" s="28" t="s">
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+    </row>
+    <row r="32" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A32" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-    </row>
-    <row r="25" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A25" s="35" t="s">
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A33" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B33" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="35" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E33" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F33" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G33" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H33" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="42"/>
-      <c r="J25" s="45" t="s">
+      <c r="I33" s="39"/>
+      <c r="J33" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="46"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A26" s="36"/>
-      <c r="B26" s="49" t="s">
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A34" s="34"/>
+      <c r="B34" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C34" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="48"/>
-    </row>
-    <row r="27" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A27" s="37"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="15" t="s">
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="45"/>
+    </row>
+    <row r="35" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A35" s="35"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="6"/>
+    <row r="36" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A36" s="19"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A37" s="19"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A38" s="19"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A39" s="19"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="J33:K34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="J23:K24"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G23:I25"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="C13:C14"/>
@@ -1552,32 +1745,16 @@
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:K13"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="J19:K20"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="G19:I21"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:I26"/>
-    <mergeCell ref="J25:K26"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -1607,164 +1784,164 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="24"/>
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="30" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="30"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="26" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="35" t="s">
+      <c r="C11" s="37"/>
+      <c r="D11" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="42"/>
-      <c r="J11" s="45" t="s">
+      <c r="I11" s="39"/>
+      <c r="J11" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="46"/>
+      <c r="K11" s="43"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="48"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="45"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="3" t="s">
         <v>1</v>
       </c>
@@ -2065,159 +2242,159 @@
       <c r="K35" s="6"/>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26" t="s">
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26" t="s">
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="26"/>
+      <c r="J37" s="24"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="30" t="s">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="30"/>
+      <c r="J38" s="26"/>
       <c r="K38" s="16"/>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="26" t="s">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="26"/>
+      <c r="J39" s="24"/>
       <c r="K39" s="16"/>
     </row>
     <row r="40" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="34"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="59"/>
     </row>
     <row r="42" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="35" t="s">
+      <c r="C42" s="37"/>
+      <c r="D42" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="35" t="s">
+      <c r="F42" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="50" t="s">
+      <c r="G42" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="41"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="45" t="s">
+      <c r="H42" s="46"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="46"/>
+      <c r="K42" s="43"/>
     </row>
     <row r="43" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A43" s="36"/>
-      <c r="B43" s="49" t="s">
+      <c r="A43" s="34"/>
+      <c r="B43" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="49" t="s">
+      <c r="C43" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="48"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="45"/>
     </row>
     <row r="44" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="37"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="44"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="41"/>
       <c r="J44" s="4" t="s">
         <v>4</v>
       </c>
@@ -2232,9 +2409,9 @@
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="22"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="56"/>
       <c r="J45" s="8"/>
       <c r="K45" s="6"/>
     </row>
@@ -2245,9 +2422,9 @@
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="22"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="56"/>
       <c r="J46" s="8"/>
       <c r="K46" s="6"/>
     </row>
@@ -2258,9 +2435,9 @@
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="22"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="56"/>
       <c r="J47" s="8"/>
       <c r="K47" s="6"/>
     </row>
@@ -2271,9 +2448,9 @@
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="22"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="56"/>
       <c r="J48" s="8"/>
       <c r="K48" s="6"/>
     </row>
@@ -2284,9 +2461,9 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="22"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="56"/>
       <c r="J49" s="8"/>
       <c r="K49" s="6"/>
     </row>
@@ -2297,9 +2474,9 @@
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="25"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="62"/>
       <c r="J50" s="8"/>
       <c r="K50" s="6"/>
     </row>
@@ -2310,9 +2487,9 @@
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="25"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="62"/>
       <c r="J51" s="8"/>
       <c r="K51" s="6"/>
     </row>
@@ -2323,9 +2500,9 @@
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="25"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="62"/>
       <c r="J52" s="8"/>
       <c r="K52" s="6"/>
     </row>
@@ -2336,9 +2513,9 @@
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="25"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="62"/>
       <c r="J53" s="8"/>
       <c r="K53" s="6"/>
     </row>
@@ -2349,96 +2526,96 @@
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="25"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="62"/>
       <c r="J54" s="8"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
     </row>
     <row r="56" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
     </row>
     <row r="57" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="38" t="s">
+      <c r="B57" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="39"/>
-      <c r="D57" s="35" t="s">
+      <c r="C57" s="37"/>
+      <c r="D57" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="35" t="s">
+      <c r="E57" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="40" t="s">
+      <c r="G57" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="H57" s="41" t="s">
+      <c r="H57" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="42"/>
-      <c r="J57" s="45" t="s">
+      <c r="I57" s="39"/>
+      <c r="J57" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="46"/>
+      <c r="K57" s="43"/>
     </row>
     <row r="58" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A58" s="36"/>
-      <c r="B58" s="49" t="s">
+      <c r="A58" s="34"/>
+      <c r="B58" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="49" t="s">
+      <c r="C58" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="47"/>
-      <c r="K58" s="48"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="45"/>
     </row>
     <row r="59" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A59" s="37"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="40"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="52"/>
       <c r="H59" s="15" t="s">
         <v>1</v>
       </c>
@@ -2558,48 +2735,14 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="H57:I58"/>
-    <mergeCell ref="J57:K58"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G42:I44"/>
-    <mergeCell ref="J42:K43"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:H8"/>
@@ -2616,14 +2759,48 @@
     <mergeCell ref="J11:K12"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="G42:I44"/>
+    <mergeCell ref="J42:K43"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="H57:I58"/>
+    <mergeCell ref="J57:K58"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>

--- a/public/templates/leave-card.xlsx
+++ b/public/templates/leave-card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIS\LMS\spana-yt\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548E7264-7798-4974-8C39-C24873481B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69665B5B-B9A4-4E48-9B5E-638F909ED0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -526,15 +526,105 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -550,99 +640,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -652,11 +649,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1136,107 +1139,107 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24" t="s">
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="24"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="26" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="24" t="s">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="24"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
     </row>
     <row r="11" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
@@ -1258,36 +1261,36 @@
       <c r="G12" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="42" t="s">
+      <c r="I12" s="40"/>
+      <c r="J12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="43"/>
+      <c r="K12" s="44"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="34"/>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="46"/>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="35"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
       <c r="D14" s="35"/>
       <c r="E14" s="35"/>
       <c r="F14" s="35"/>
@@ -1315,7 +1318,7 @@
       <c r="G15" s="19"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="63"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
@@ -1328,7 +1331,7 @@
       <c r="G16" s="19"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="63"/>
+      <c r="J16" s="22"/>
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
@@ -1341,7 +1344,7 @@
       <c r="G17" s="19"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="63"/>
+      <c r="J17" s="22"/>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
@@ -1354,7 +1357,7 @@
       <c r="G18" s="19"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="63"/>
+      <c r="J18" s="22"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="31.35" customHeight="1" x14ac:dyDescent="0.65">
@@ -1371,51 +1374,51 @@
       <c r="K19" s="6"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="59"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A23" s="33" t="s">
@@ -1434,43 +1437,43 @@
       <c r="F23" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42" t="s">
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="43"/>
+      <c r="K23" s="44"/>
     </row>
     <row r="24" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A24" s="34"/>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="45"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="46"/>
     </row>
     <row r="25" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A25" s="35"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
       <c r="D25" s="35"/>
       <c r="E25" s="35"/>
       <c r="F25" s="35"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="41"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
       <c r="J25" s="4" t="s">
         <v>4</v>
       </c>
@@ -1482,52 +1485,52 @@
       <c r="A26" s="19"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="63"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="22"/>
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A27" s="19"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="63"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="22"/>
       <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A28" s="19"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="63"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="22"/>
       <c r="K28" s="4"/>
     </row>
     <row r="29" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A29" s="19"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="63"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -1537,41 +1540,41 @@
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="56"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
       <c r="J30" s="8"/>
       <c r="K30" s="6"/>
     </row>
     <row r="31" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
     </row>
     <row r="32" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
     </row>
     <row r="33" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A33" s="33" t="s">
@@ -1590,43 +1593,43 @@
       <c r="F33" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G33" s="52" t="s">
+      <c r="G33" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H33" s="46" t="s">
+      <c r="H33" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="I33" s="39"/>
-      <c r="J33" s="42" t="s">
+      <c r="I33" s="40"/>
+      <c r="J33" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="43"/>
+      <c r="K33" s="44"/>
     </row>
     <row r="34" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A34" s="34"/>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
       <c r="F34" s="34"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="45"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="46"/>
     </row>
     <row r="35" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A35" s="35"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
       <c r="D35" s="35"/>
       <c r="E35" s="35"/>
       <c r="F35" s="35"/>
-      <c r="G35" s="52"/>
+      <c r="G35" s="38"/>
       <c r="H35" s="15" t="s">
         <v>1</v>
       </c>
@@ -1644,52 +1647,52 @@
       <c r="A36" s="19"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="20"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="63"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="22"/>
       <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="19"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
       <c r="G37" s="20"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="63"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="22"/>
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A38" s="19"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="20"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="63"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="22"/>
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A39" s="19"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="20"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="63"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="22"/>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -1700,21 +1703,37 @@
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="9"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="8"/>
       <c r="K40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="B22:K22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:D25"/>
+  <mergeCells count="52">
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:K13"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:D14"/>
     <mergeCell ref="A31:K31"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="A33:A35"/>
@@ -1727,6 +1746,14 @@
     <mergeCell ref="J33:K34"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:D25"/>
     <mergeCell ref="E23:E25"/>
     <mergeCell ref="F23:F25"/>
     <mergeCell ref="J23:K24"/>
@@ -1735,26 +1762,6 @@
     <mergeCell ref="G23:I25"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:K13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -1784,109 +1791,109 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24" t="s">
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="24"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="26" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="24" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="24"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
     </row>
     <row r="10" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
@@ -1908,36 +1915,36 @@
       <c r="G11" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="42" t="s">
+      <c r="I11" s="40"/>
+      <c r="J11" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="43"/>
+      <c r="K11" s="44"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="45"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="35"/>
       <c r="E13" s="35"/>
       <c r="F13" s="35"/>
@@ -2242,104 +2249,104 @@
       <c r="K35" s="6"/>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24" t="s">
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="24"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="26" t="s">
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="26"/>
+      <c r="J38" s="56"/>
       <c r="K38" s="16"/>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="24" t="s">
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="24"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="16"/>
     </row>
     <row r="40" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="59"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="32"/>
     </row>
     <row r="42" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A42" s="33" t="s">
@@ -2358,43 +2365,43 @@
       <c r="F42" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="42" t="s">
+      <c r="H42" s="39"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="43"/>
+      <c r="K42" s="44"/>
     </row>
     <row r="43" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A43" s="34"/>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="34"/>
       <c r="E43" s="34"/>
       <c r="F43" s="34"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="46"/>
     </row>
     <row r="44" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="35"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
       <c r="D44" s="35"/>
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="41"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="42"/>
       <c r="J44" s="4" t="s">
         <v>4</v>
       </c>
@@ -2409,9 +2416,9 @@
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="56"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26"/>
       <c r="J45" s="8"/>
       <c r="K45" s="6"/>
     </row>
@@ -2422,9 +2429,9 @@
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="56"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
       <c r="J46" s="8"/>
       <c r="K46" s="6"/>
     </row>
@@ -2435,9 +2442,9 @@
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="56"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26"/>
       <c r="J47" s="8"/>
       <c r="K47" s="6"/>
     </row>
@@ -2448,9 +2455,9 @@
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="56"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="26"/>
       <c r="J48" s="8"/>
       <c r="K48" s="6"/>
     </row>
@@ -2461,9 +2468,9 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="56"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="26"/>
       <c r="J49" s="8"/>
       <c r="K49" s="6"/>
     </row>
@@ -2474,9 +2481,9 @@
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
-      <c r="G50" s="60"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="62"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="61"/>
       <c r="J50" s="8"/>
       <c r="K50" s="6"/>
     </row>
@@ -2487,9 +2494,9 @@
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="62"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="60"/>
+      <c r="I51" s="61"/>
       <c r="J51" s="8"/>
       <c r="K51" s="6"/>
     </row>
@@ -2500,9 +2507,9 @@
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
-      <c r="G52" s="60"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="62"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="61"/>
       <c r="J52" s="8"/>
       <c r="K52" s="6"/>
     </row>
@@ -2513,9 +2520,9 @@
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
-      <c r="G53" s="60"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="62"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="60"/>
+      <c r="I53" s="61"/>
       <c r="J53" s="8"/>
       <c r="K53" s="6"/>
     </row>
@@ -2526,41 +2533,41 @@
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
-      <c r="G54" s="60"/>
-      <c r="H54" s="61"/>
-      <c r="I54" s="62"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="60"/>
+      <c r="I54" s="61"/>
       <c r="J54" s="8"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A55" s="51" t="s">
+      <c r="A55" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="51"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+      <c r="K55" s="27"/>
     </row>
     <row r="56" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="29"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
     </row>
     <row r="57" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A57" s="33" t="s">
@@ -2579,43 +2586,43 @@
       <c r="F57" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="52" t="s">
+      <c r="G57" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H57" s="46" t="s">
+      <c r="H57" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="39"/>
-      <c r="J57" s="42" t="s">
+      <c r="I57" s="40"/>
+      <c r="J57" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="43"/>
+      <c r="K57" s="44"/>
     </row>
     <row r="58" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A58" s="34"/>
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C58" s="47" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="34"/>
       <c r="F58" s="34"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="45"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="46"/>
     </row>
     <row r="59" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A59" s="35"/>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="47"/>
       <c r="D59" s="35"/>
       <c r="E59" s="35"/>
       <c r="F59" s="35"/>
-      <c r="G59" s="52"/>
+      <c r="G59" s="38"/>
       <c r="H59" s="15" t="s">
         <v>1</v>
       </c>
@@ -2735,14 +2742,48 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="H57:I58"/>
+    <mergeCell ref="J57:K58"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="G42:I44"/>
+    <mergeCell ref="J42:K43"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:H8"/>
@@ -2759,48 +2800,14 @@
     <mergeCell ref="J11:K12"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G42:I44"/>
-    <mergeCell ref="J42:K43"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="H57:I58"/>
-    <mergeCell ref="J57:K58"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>

--- a/public/templates/leave-card.xlsx
+++ b/public/templates/leave-card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIS\LMS\spana-yt\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69665B5B-B9A4-4E48-9B5E-638F909ED0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B347F577-BACC-4E42-B4DD-FF8066110DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -532,9 +532,126 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,123 +660,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,162 +1139,162 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54" t="s">
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="54"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="56" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="56"/>
+      <c r="J8" s="28"/>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="54" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="26"/>
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
     </row>
     <row r="11" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="44"/>
+      <c r="D12" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="48" t="s">
+      <c r="H12" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="40"/>
-      <c r="J12" s="43" t="s">
+      <c r="I12" s="35"/>
+      <c r="J12" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="44"/>
+      <c r="K12" s="39"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="47" t="s">
+      <c r="A13" s="32"/>
+      <c r="B13" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="46"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1374,106 +1374,106 @@
       <c r="K19" s="6"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="32"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="55"/>
     </row>
     <row r="23" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="33" t="s">
+      <c r="C23" s="44"/>
+      <c r="D23" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="43" t="s">
+      <c r="H23" s="49"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="44"/>
+      <c r="K23" s="39"/>
     </row>
     <row r="24" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A24" s="34"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="32"/>
+      <c r="B24" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="46"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A25" s="35"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="4" t="s">
         <v>4</v>
       </c>
@@ -1488,9 +1488,9 @@
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="25"/>
       <c r="J26" s="22"/>
       <c r="K26" s="4"/>
     </row>
@@ -1501,9 +1501,9 @@
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="25"/>
       <c r="J27" s="22"/>
       <c r="K27" s="4"/>
     </row>
@@ -1514,9 +1514,9 @@
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25"/>
       <c r="J28" s="22"/>
       <c r="K28" s="4"/>
     </row>
@@ -1527,9 +1527,9 @@
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25"/>
       <c r="J29" s="22"/>
       <c r="K29" s="4"/>
     </row>
@@ -1540,96 +1540,96 @@
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
       <c r="J30" s="8"/>
       <c r="K30" s="6"/>
     </row>
     <row r="31" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
     </row>
     <row r="32" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
     </row>
     <row r="33" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33" t="s">
+      <c r="C33" s="44"/>
+      <c r="D33" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="H33" s="39" t="s">
+      <c r="H33" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I33" s="40"/>
-      <c r="J33" s="43" t="s">
+      <c r="I33" s="35"/>
+      <c r="J33" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="44"/>
+      <c r="K33" s="39"/>
     </row>
     <row r="34" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A34" s="34"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="32"/>
+      <c r="B34" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="46"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="41"/>
     </row>
     <row r="35" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A35" s="35"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="38"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="48"/>
       <c r="H35" s="15" t="s">
         <v>1</v>
       </c>
@@ -1710,42 +1710,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:K13"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="A31:K31"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="J33:K34"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="A20:K20"/>
@@ -1762,6 +1726,42 @@
     <mergeCell ref="G23:I25"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="J33:K34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="J12:K13"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="H12:I13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -1791,164 +1791,164 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.65">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54" t="s">
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="54"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="56" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="56"/>
+      <c r="J7" s="28"/>
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="54" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="54"/>
+      <c r="J8" s="26"/>
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
     </row>
     <row r="10" spans="1:11" s="14" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="33" t="s">
+      <c r="C11" s="44"/>
+      <c r="D11" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="43" t="s">
+      <c r="I11" s="35"/>
+      <c r="J11" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="44"/>
+      <c r="K11" s="39"/>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="47" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="46"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="41"/>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
       <c r="H13" s="3" t="s">
         <v>1</v>
       </c>
@@ -2249,159 +2249,159 @@
       <c r="K35" s="6"/>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54" t="s">
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="54"/>
+      <c r="J37" s="26"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="56" t="s">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="56"/>
+      <c r="J38" s="28"/>
       <c r="K38" s="16"/>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="54" t="s">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="54"/>
+      <c r="J39" s="26"/>
       <c r="K39" s="16"/>
     </row>
     <row r="40" spans="1:11" s="1" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="47"/>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="32"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="55"/>
     </row>
     <row r="42" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="33" t="s">
+      <c r="C42" s="44"/>
+      <c r="D42" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="39"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="43" t="s">
+      <c r="H42" s="49"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="44"/>
+      <c r="K42" s="39"/>
     </row>
     <row r="43" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A43" s="34"/>
-      <c r="B43" s="47" t="s">
+      <c r="A43" s="32"/>
+      <c r="B43" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="46"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="41"/>
     </row>
     <row r="44" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="35"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="42"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="37"/>
       <c r="J44" s="4" t="s">
         <v>4</v>
       </c>
@@ -2416,9 +2416,9 @@
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="26"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="65"/>
       <c r="J45" s="8"/>
       <c r="K45" s="6"/>
     </row>
@@ -2429,9 +2429,9 @@
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="26"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
       <c r="J46" s="8"/>
       <c r="K46" s="6"/>
     </row>
@@ -2442,9 +2442,9 @@
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="26"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65"/>
       <c r="J47" s="8"/>
       <c r="K47" s="6"/>
     </row>
@@ -2455,9 +2455,9 @@
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="26"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65"/>
       <c r="J48" s="8"/>
       <c r="K48" s="6"/>
     </row>
@@ -2468,9 +2468,9 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="26"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="65"/>
       <c r="J49" s="8"/>
       <c r="K49" s="6"/>
     </row>
@@ -2481,9 +2481,9 @@
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="60"/>
-      <c r="I50" s="61"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="62"/>
       <c r="J50" s="8"/>
       <c r="K50" s="6"/>
     </row>
@@ -2494,9 +2494,9 @@
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="61"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="62"/>
       <c r="J51" s="8"/>
       <c r="K51" s="6"/>
     </row>
@@ -2507,9 +2507,9 @@
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="60"/>
-      <c r="I52" s="61"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="62"/>
       <c r="J52" s="8"/>
       <c r="K52" s="6"/>
     </row>
@@ -2520,9 +2520,9 @@
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="61"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="62"/>
       <c r="J53" s="8"/>
       <c r="K53" s="6"/>
     </row>
@@ -2533,96 +2533,96 @@
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="60"/>
-      <c r="I54" s="61"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="62"/>
       <c r="J54" s="8"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
     </row>
     <row r="56" spans="1:11" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="47"/>
+      <c r="K56" s="47"/>
     </row>
     <row r="57" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A57" s="33" t="s">
+      <c r="A57" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="37"/>
-      <c r="D57" s="33" t="s">
+      <c r="C57" s="44"/>
+      <c r="D57" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="33" t="s">
+      <c r="E57" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="33" t="s">
+      <c r="F57" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="43" t="s">
+      <c r="I57" s="35"/>
+      <c r="J57" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="44"/>
+      <c r="K57" s="39"/>
     </row>
     <row r="58" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A58" s="34"/>
-      <c r="B58" s="47" t="s">
+      <c r="A58" s="32"/>
+      <c r="B58" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="47" t="s">
+      <c r="C58" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="46"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A59" s="35"/>
-      <c r="B59" s="47"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="38"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="48"/>
       <c r="H59" s="15" t="s">
         <v>1</v>
       </c>
@@ -2742,48 +2742,14 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="H57:I58"/>
-    <mergeCell ref="J57:K58"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G42:I44"/>
-    <mergeCell ref="J42:K43"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:H8"/>
@@ -2800,14 +2766,48 @@
     <mergeCell ref="J11:K12"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="G42:I44"/>
+    <mergeCell ref="J42:K43"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="H57:I58"/>
+    <mergeCell ref="J57:K58"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
